--- a/Documents/Salary Grade Matrix.xlsx
+++ b/Documents/Salary Grade Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60ADBDB7-F421-42A2-A85B-B917A3543B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26513535-8AC6-4E67-AB32-5AC22A3DE44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{483A9092-D30C-44D8-BF1D-8032B11A5C33}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{483A9092-D30C-44D8-BF1D-8032B11A5C33}"/>
   </bookViews>
   <sheets>
     <sheet name="SalaryGrade" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12978" uniqueCount="6077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12971" uniqueCount="6077">
   <si>
     <t>Name</t>
   </si>
@@ -21100,7 +21100,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>88</v>
       </c>
@@ -21117,7 +21117,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>88</v>
       </c>
@@ -21134,7 +21134,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>88</v>
       </c>
@@ -21151,7 +21151,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>88</v>
       </c>
@@ -21168,7 +21168,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>88</v>
       </c>
@@ -21185,7 +21185,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>88</v>
       </c>
@@ -21202,7 +21202,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>88</v>
       </c>
@@ -21219,7 +21219,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>88</v>
       </c>
@@ -21236,7 +21236,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>88</v>
       </c>
@@ -21258,11 +21258,6 @@
     <filterColumn colId="0">
       <filters>
         <filter val="UNILAB, Inc."/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="NON-KP"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -61825,7 +61820,7 @@
   <cols>
     <col min="1" max="1" width="16.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.26953125" customWidth="1"/>
-    <col min="3" max="3" width="16.90625" customWidth="1"/>
+    <col min="3" max="3" width="16.90625" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="11.54296875" customWidth="1"/>
     <col min="5" max="5" width="11.7265625" customWidth="1"/>
     <col min="6" max="6" width="12.6328125" customWidth="1"/>
@@ -61942,11 +61937,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D2" t="str">
-        <f>"Insert Into SalaryGrades(TypeId,GradeName) Values(1,'"&amp;B2&amp;"');"</f>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'5');</v>
+        <f>"Insert Into SalaryGrades(TypeId,GradeName) Values(2,'"&amp;B2&amp;"');"</f>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'AM');</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -61954,11 +61949,11 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D3" t="str">
-        <f t="shared" ref="D3:D17" si="0">"Insert Into SalaryGrades(TypeId,GradeName) Values(1,'"&amp;B3&amp;"');"</f>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'6');</v>
+        <f t="shared" ref="D3:D17" si="0">"Insert Into SalaryGrades(TypeId,GradeName) Values(2,'"&amp;B3&amp;"');"</f>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'KP-MGR');</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -61966,11 +61961,11 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="D4" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'7');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'KP-SRM');</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -61978,11 +61973,11 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'8');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'KP-DIR');</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -61990,11 +61985,11 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'9');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'KP-AVP');</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -62002,11 +61997,11 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'10');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'KP-DVP');</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -62014,11 +62009,11 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D8" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'S1');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'KP-OVP');</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -62026,11 +62021,11 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D9" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'S1-C');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'KP-CVP');</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -62038,95 +62033,81 @@
         <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'S2');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'KP-SVP');</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>77</v>
-      </c>
+      <c r="B11" s="2"/>
       <c r="D11" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'S2-C');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'');</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>78</v>
-      </c>
+      <c r="B12" s="2"/>
       <c r="D12" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'S3');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'');</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>79</v>
-      </c>
+      <c r="B13" s="2"/>
       <c r="D13" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'S3-C');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'');</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="B14" s="2"/>
       <c r="D14" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'S4');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'');</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>81</v>
-      </c>
+      <c r="B15" s="2"/>
       <c r="D15" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'S4-C');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'');</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="B16" s="2"/>
       <c r="D16" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'S5');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'');</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>83</v>
-      </c>
+      <c r="B17" s="2"/>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
-        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(1,'S5-C');</v>
+        <v>Insert Into SalaryGrades(TypeId,GradeName) Values(2,'');</v>
       </c>
     </row>
   </sheetData>
